--- a/utility/test.xlsx
+++ b/utility/test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SusmitSurwade\IdeaProjects\orange_hrms_trial_app\utility\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\IdeaProjects\orange_hrms_trial_app\utility\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F98DC18-741C-4B47-9774-6879954267E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B503AD-3FEE-485A-8CBA-3B9DE159DD47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -89,7 +78,7 @@
     <t>Belgian</t>
   </si>
   <si>
-    <t>aH5o@UmNP5</t>
+    <t>Y@dpQhI2L3</t>
   </si>
 </sst>
 </file>
